--- a/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SAN MARCOS DEL SUR</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.27866</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.86653</v>
-      </c>
-      <c r="I2" t="n">
-        <v>248</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.27866</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.86653</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>83 MI JESUS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.25131</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.89708</v>
-      </c>
-      <c r="I3" t="n">
-        <v>336</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.25131</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.89708</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>657 EMILIA BARCIA BONIFATTI</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.27182</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.86933999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>204</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.27182</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.86934</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>660 NIÑOS DE BELEN / 7264 DR MANUEL MIGUEL VALLE Y VALLE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.25571</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.87459</v>
-      </c>
-      <c r="I5" t="n">
-        <v>319</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.25571</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.87459</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>7104 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.24331</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.87348</v>
-      </c>
-      <c r="I6" t="n">
-        <v>409</v>
-      </c>
-      <c r="J6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.24331</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.87348</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>7098 RODRIGO LARA BONILLA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.23534</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.90897</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1712</v>
-      </c>
-      <c r="J7" t="n">
-        <v>72</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.23534</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.90897</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>7056 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.27407</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.87130000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1124</v>
-      </c>
-      <c r="J8" t="n">
-        <v>39</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.27407</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.8713</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>6031 SANTA MARIA DE LURIN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.27448</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.87103</v>
-      </c>
-      <c r="I9" t="n">
-        <v>877</v>
-      </c>
-      <c r="J9" t="n">
-        <v>34</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.27448</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.87103</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>6008 JOSE ANTONIO DAPELO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.2737</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.87177</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1693</v>
-      </c>
-      <c r="J10" t="n">
-        <v>64</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.2737</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.87177</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>6023 JULIO C TELLO ROJAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.24729</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.89738</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J11" t="n">
-        <v>60</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.24729</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.89738</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>6026 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.25174</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.89713999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>723</v>
-      </c>
-      <c r="J12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.25174</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.89714</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>7078 VIRGEN DE CHAPI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.25227</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.88056</v>
-      </c>
-      <c r="I13" t="n">
-        <v>274</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.25227</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.88056</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>7085 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.2604</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.88798</v>
-      </c>
-      <c r="I14" t="n">
-        <v>340</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.2604</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.88798</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.277363</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.867638</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1531</v>
-      </c>
-      <c r="J15" t="n">
-        <v>83</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.277363</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.867638</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.2934</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.85762</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1257</v>
-      </c>
-      <c r="J16" t="n">
-        <v>47</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.2934</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.85762</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>JHON F. KENNEDY</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.2755</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.86712</v>
-      </c>
-      <c r="I17" t="n">
-        <v>226</v>
-      </c>
-      <c r="J17" t="n">
-        <v>22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.2755</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.86712</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.23442</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.91038</v>
-      </c>
-      <c r="I18" t="n">
-        <v>218</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.23442</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.91038</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.278</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.86609</v>
-      </c>
-      <c r="I19" t="n">
-        <v>507</v>
-      </c>
-      <c r="J19" t="n">
-        <v>34</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.278</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.86609</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>7258</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.2274</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.89060000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>337</v>
-      </c>
-      <c r="J20" t="n">
-        <v>13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.2274</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.8906</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>7239 SANTISIMO SALVADOR</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.23333</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.89234999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>925</v>
-      </c>
-      <c r="J21" t="n">
-        <v>42</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.23333</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.89235</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>20915</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.222213</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.8433</v>
-      </c>
-      <c r="I22" t="n">
-        <v>627</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.222213</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.8433</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>LA ROCA CHRISTIAN SCHOOL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.22715</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.90184000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>330</v>
-      </c>
-      <c r="J23" t="n">
-        <v>30</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.22715</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.90184</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>LALITO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.27223</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.86761</v>
-      </c>
-      <c r="I24" t="n">
-        <v>437</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.27223</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.86761</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>HAPPY CHILDREN SCHOOL</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.28869</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.85213</v>
-      </c>
-      <c r="I25" t="n">
-        <v>254</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.28869</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.85213</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>JOSE ABELARDO QUIÑONES DE LURIN</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.23437</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.90985000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>265</v>
-      </c>
-      <c r="J26" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.23437</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.90985</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>TRAVESURAS TRAZOS Y COLORES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.28818</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.8528</v>
-      </c>
-      <c r="I27" t="n">
-        <v>555</v>
-      </c>
-      <c r="J27" t="n">
-        <v>33</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.28818</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.8528</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>82 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.272446</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.867993</v>
-      </c>
-      <c r="I28" t="n">
-        <v>255</v>
-      </c>
-      <c r="J28" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.272446</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.867993</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>7267 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.23471</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.90577999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>410</v>
-      </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.23471</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.90578</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>HUELLITAS DE JESUS</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.27595</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.86763000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>326</v>
-      </c>
-      <c r="J30" t="n">
-        <v>25</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.27595</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.86763</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>VIRGEN DE COCHARCAS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.24834</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.89721</v>
-      </c>
-      <c r="I31" t="n">
-        <v>221</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.24834</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.89721</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>VICTORIA SCHOOL</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.29173</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.85724</v>
-      </c>
-      <c r="I32" t="n">
-        <v>283</v>
-      </c>
-      <c r="J32" t="n">
-        <v>16</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.29173</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.85724</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SAN MARCOS DEL SUR</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.27922</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.86564</v>
-      </c>
-      <c r="I33" t="n">
-        <v>254</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.27922</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.86564</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SACO OLIVEROS DE LURIN</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.28008</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.86503999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>558</v>
-      </c>
-      <c r="J34" t="n">
-        <v>28</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.28008</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.86504</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.27236</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.86767</v>
-      </c>
-      <c r="I35" t="n">
-        <v>361</v>
-      </c>
-      <c r="J35" t="n">
-        <v>14</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.27236</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.86767</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>SAN JUAN DE LA CRUZ DE LURIN</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.2906</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.85847</v>
-      </c>
-      <c r="I36" t="n">
-        <v>330</v>
-      </c>
-      <c r="J36" t="n">
-        <v>25</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.2906</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.85847</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>COPRODELI CRISTO SACERDOTE</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.237242</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.90639299999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>321</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.237242</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.906393</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>INICIAL CARPE DIEM LURIN</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.277431</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.866573</v>
-      </c>
-      <c r="I38" t="n">
-        <v>108</v>
-      </c>
-      <c r="J38" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.277431</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.866573</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>245125</t>
+          <t>686736</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN MARCOS DEL SUR</t>
+          <t>82 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.27866</t>
+          <t>-12.272446</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.86653</t>
+          <t>-76.867993</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>314915</t>
+          <t>314920</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>657 EMILIA BARCIA BONIFATTI</t>
+          <t>660 NIÑOS DE BELEN / 7264 DR MANUEL MIGUEL VALLE Y VALLE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.27182</t>
+          <t>-12.25571</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.86934</t>
+          <t>-76.87459</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>314920</t>
+          <t>315024</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>660 NIÑOS DE BELEN / 7264 DR MANUEL MIGUEL VALLE Y VALLE</t>
+          <t>7078 VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.25571</t>
+          <t>-12.25227</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.87459</t>
+          <t>-76.88056</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>318268</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7104 RAMIRO PRIALE PRIALE</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.24331</t>
+          <t>-12.2274</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.87348</t>
+          <t>-76.8906</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>812136</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7098 RODRIGO LARA BONILLA</t>
+          <t>SAN MARCOS DEL SUR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.23534</t>
+          <t>-12.27922</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.90897</t>
+          <t>-76.86564</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>314963</t>
+          <t>827557</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7056 SAN MARTIN DE PORRES</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.27407</t>
+          <t>-12.27236</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.8713</t>
+          <t>-76.86767</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>314977</t>
+          <t>804136</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6031 SANTA MARIA DE LURIN</t>
+          <t>VICTORIA SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.27448</t>
+          <t>-12.29173</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.87103</t>
+          <t>-76.85724</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>314982</t>
+          <t>245125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6008 JOSE ANTONIO DAPELO</t>
+          <t>SAN MARCOS DEL SUR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.2737</t>
+          <t>-12.27866</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.87177</t>
+          <t>-76.86653</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>315000</t>
+          <t>315038</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6023 JULIO C TELLO ROJAS</t>
+          <t>7085 SANTA ROSA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.24729</t>
+          <t>-12.2604</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.89738</t>
+          <t>-76.88798</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>315019</t>
+          <t>314939</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6026 VIRGEN DE FATIMA</t>
+          <t>7104 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.25174</t>
+          <t>-12.24331</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.89714</t>
+          <t>-76.87348</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>315024</t>
+          <t>536431</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7078 VIRGEN DE CHAPI</t>
+          <t>LALITO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.25227</t>
+          <t>-12.27223</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.88056</t>
+          <t>-76.86761</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>437</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>315038</t>
+          <t>572985</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7085 SANTA ROSA</t>
+          <t>JOSE ABELARDO QUIÑONES DE LURIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.2604</t>
+          <t>-12.23437</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.88798</t>
+          <t>-76.90985</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>315043</t>
+          <t>687887</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>7267 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.277363</t>
+          <t>-12.23471</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.867638</t>
+          <t>-76.90578</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>315062</t>
+          <t>315104</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU SEMINARIO</t>
+          <t>JHON F. KENNEDY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.2934</t>
+          <t>-12.2755</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.85762</t>
+          <t>-76.86712</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>315104</t>
+          <t>556928</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JHON F. KENNEDY</t>
+          <t>HAPPY CHILDREN SCHOOL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.2755</t>
+          <t>-12.28869</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.86712</t>
+          <t>-76.85213</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>315118</t>
+          <t>688170</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>REYNA DE LOS ANGELES</t>
+          <t>VIRGEN DE COCHARCAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.23442</t>
+          <t>-12.24834</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.91038</t>
+          <t>-76.89721</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>315142</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.278</t>
+          <t>-12.23442</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.86609</t>
+          <t>-76.91038</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>318268</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>COPRODELI CRISTO SACERDOTE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.2274</t>
+          <t>-12.237242</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.8906</t>
+          <t>-76.906393</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>318348</t>
+          <t>688066</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7239 SANTISIMO SALVADOR</t>
+          <t>HUELLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.23333</t>
+          <t>-12.27595</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.89235</t>
+          <t>-76.86763</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>358867</t>
+          <t>836868</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>SAN JUAN DE LA CRUZ DE LURIN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.222213</t>
+          <t>-12.2906</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.8433</t>
+          <t>-76.85847</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>518842</t>
+          <t>315019</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LA ROCA CHRISTIAN SCHOOL</t>
+          <t>6026 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.22715</t>
+          <t>-12.25174</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.90184</t>
+          <t>-76.89714</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>723</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>536431</t>
+          <t>358867</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LALITO</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.27223</t>
+          <t>-12.222213</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.86761</t>
+          <t>-76.8433</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>627</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>556928</t>
+          <t>824064</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HAPPY CHILDREN SCHOOL</t>
+          <t>SACO OLIVEROS DE LURIN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.28869</t>
+          <t>-12.28008</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.85213</t>
+          <t>-76.86504</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>558</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>572985</t>
+          <t>518842</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JOSE ABELARDO QUIÑONES DE LURIN</t>
+          <t>LA ROCA CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.23437</t>
+          <t>-12.22715</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.90985</t>
+          <t>-76.90184</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>686736</t>
+          <t>314977</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>82 SAGRADO CORAZON DE JESUS</t>
+          <t>6031 SANTA MARIA DE LURIN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.272446</t>
+          <t>-12.27448</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.867993</t>
+          <t>-76.87103</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>877</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>687887</t>
+          <t>315142</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7267 SEÑOR DE LOS MILAGROS</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.23471</t>
+          <t>-12.278</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.90578</t>
+          <t>-76.86609</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>507</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>688066</t>
+          <t>314963</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HUELLITAS DE JESUS</t>
+          <t>7056 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.27595</t>
+          <t>-12.27407</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.86763</t>
+          <t>-76.8713</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>688170</t>
+          <t>318348</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VIRGEN DE COCHARCAS</t>
+          <t>7239 SANTISIMO SALVADOR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.24834</t>
+          <t>-12.23333</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.89721</t>
+          <t>-76.89235</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>804136</t>
+          <t>315062</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VICTORIA SCHOOL</t>
+          <t>MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.29173</t>
+          <t>-12.2934</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.85724</t>
+          <t>-76.85762</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>812136</t>
+          <t>904555</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN MARCOS DEL SUR</t>
+          <t>INICIAL CARPE DIEM LURIN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.27922</t>
+          <t>-12.277431</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.86564</t>
+          <t>-76.866573</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>824064</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE LURIN</t>
+          <t>6023 JULIO C TELLO ROJAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.28008</t>
+          <t>-12.24729</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.86504</t>
+          <t>-76.89738</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>827557</t>
+          <t>314982</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>6008 JOSE ANTONIO DAPELO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.27236</t>
+          <t>-12.2737</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.86767</t>
+          <t>-76.87177</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>836868</t>
+          <t>314958</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LA CRUZ DE LURIN</t>
+          <t>7098 RODRIGO LARA BONILLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.2906</t>
+          <t>-12.23534</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.85847</t>
+          <t>-76.90897</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>904490</t>
+          <t>315043</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>COPRODELI CRISTO SACERDOTE</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.237242</t>
+          <t>-12.277363</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.906393</t>
+          <t>-76.867638</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>904555</t>
+          <t>314915</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INICIAL CARPE DIEM LURIN</t>
+          <t>657 EMILIA BARCIA BONIFATTI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.277431</t>
+          <t>-12.27182</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.866573</t>
+          <t>-76.86934</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>686736</t>
+          <t>904555</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82 SAGRADO CORAZON DE JESUS</t>
+          <t>INICIAL CARPE DIEM LURIN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.272446</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.867993</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-12.277431</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.866573</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>314883</t>
+          <t>904490</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>83 MI JESUS</t>
+          <t>COPRODELI CRISTO SACERDOTE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.25131</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.89708</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-12.237242</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.906393</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>314920</t>
+          <t>836868</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>660 NIÑOS DE BELEN / 7264 DR MANUEL MIGUEL VALLE Y VALLE</t>
+          <t>SAN JUAN DE LA CRUZ DE LURIN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.25571</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.87459</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-12.2906</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.85847</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>315024</t>
+          <t>827557</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7078 VIRGEN DE CHAPI</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.25227</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.88056</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-12.27236</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.86767</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>318268</t>
+          <t>824064</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>SACO OLIVEROS DE LURIN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.2274</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.8906</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-12.28008</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.86504</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>-12.27922</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-76.86564</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>827557</t>
+          <t>804136</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>VICTORIA SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.27236</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.86767</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-12.29173</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.85724</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>804136</t>
+          <t>688170</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VICTORIA SCHOOL</t>
+          <t>VIRGEN DE COCHARCAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.29173</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.85724</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-12.24834</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.89721</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>245125</t>
+          <t>688066</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN MARCOS DEL SUR</t>
+          <t>HUELLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.27866</t>
+          <t>326</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.86653</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-12.27595</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.86763</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>315038</t>
+          <t>687887</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7085 SANTA ROSA</t>
+          <t>7267 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.2604</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.88798</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-12.23471</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.90578</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>686736</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7104 RAMIRO PRIALE PRIALE</t>
+          <t>82 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.24331</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.87348</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>-12.272446</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.867993</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>536431</t>
+          <t>589151</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LALITO</t>
+          <t>TRAVESURAS TRAZOS Y COLORES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.27223</t>
+          <t>555</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.86761</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>-12.28818</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.8528</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-12.23437</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-76.90985</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>687887</t>
+          <t>556928</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7267 SEÑOR DE LOS MILAGROS</t>
+          <t>HAPPY CHILDREN SCHOOL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.23471</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.90578</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-12.28869</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.85213</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>315104</t>
+          <t>536431</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JHON F. KENNEDY</t>
+          <t>LALITO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.2755</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.86712</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.27223</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.86761</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>556928</t>
+          <t>518842</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HAPPY CHILDREN SCHOOL</t>
+          <t>LA ROCA CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.28869</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.85213</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-12.22715</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.90184</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>688170</t>
+          <t>358867</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VIRGEN DE COCHARCAS</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.24834</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.89721</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.222213</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.8433</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>315118</t>
+          <t>318348</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>REYNA DE LOS ANGELES</t>
+          <t>7239 SANTISIMO SALVADOR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.23442</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.91038</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-12.23333</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.89235</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>904490</t>
+          <t>318268</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COPRODELI CRISTO SACERDOTE</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.237242</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.906393</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>-12.2274</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.8906</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>688066</t>
+          <t>315142</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HUELLITAS DE JESUS</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.27595</t>
+          <t>507</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.86763</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>-12.278</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.86609</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>836868</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LA CRUZ DE LURIN</t>
+          <t>REYNA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.2906</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.85847</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.23442</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.91038</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>315019</t>
+          <t>315104</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6026 VIRGEN DE FATIMA</t>
+          <t>JHON F. KENNEDY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.25174</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.89714</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>-12.2755</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.86712</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>358867</t>
+          <t>315062</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.222213</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.8433</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>-12.2934</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.85762</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>824064</t>
+          <t>315043</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE LURIN</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.28008</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.86504</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>-12.277363</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.867638</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>518842</t>
+          <t>315038</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LA ROCA CHRISTIAN SCHOOL</t>
+          <t>7085 SANTA ROSA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.22715</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.90184</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.2604</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.88798</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>589151</t>
+          <t>315024</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRAVESURAS TRAZOS Y COLORES</t>
+          <t>7078 VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.28818</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.8528</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>-12.25227</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.88056</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>314977</t>
+          <t>315019</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6031 SANTA MARIA DE LURIN</t>
+          <t>6026 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.27448</t>
+          <t>723</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.87103</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>-12.25174</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.89714</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>315142</t>
+          <t>315000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>6023 JULIO C TELLO ROJAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.278</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.86609</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>-12.24729</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.89738</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>314963</t>
+          <t>314982</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7056 SAN MARTIN DE PORRES</t>
+          <t>6008 JOSE ANTONIO DAPELO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.27407</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.8713</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>-12.2737</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.87177</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>318348</t>
+          <t>314977</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7239 SANTISIMO SALVADOR</t>
+          <t>6031 SANTA MARIA DE LURIN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.23333</t>
+          <t>877</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.89235</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-12.27448</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.87103</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>315062</t>
+          <t>314963</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU SEMINARIO</t>
+          <t>7056 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.2934</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.85762</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-12.27407</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.8713</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>904555</t>
+          <t>314958</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INICIAL CARPE DIEM LURIN</t>
+          <t>7098 RODRIGO LARA BONILLA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.277431</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.866573</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>-12.23534</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.90897</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>315000</t>
+          <t>314939</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6023 JULIO C TELLO ROJAS</t>
+          <t>7104 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.24729</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.89738</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>-12.24331</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.87348</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>314982</t>
+          <t>314920</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6008 JOSE ANTONIO DAPELO</t>
+          <t>660 NIÑOS DE BELEN / 7264 DR MANUEL MIGUEL VALLE Y VALLE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.2737</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.87177</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>-12.25571</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-76.87459</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>314915</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7098 RODRIGO LARA BONILLA</t>
+          <t>657 EMILIA BARCIA BONIFATTI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.23534</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.90897</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>-12.27182</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-76.86934</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>315043</t>
+          <t>314883</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>83 MI JESUS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.277363</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.867638</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>-12.25131</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-76.89708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>314915</t>
+          <t>245125</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>657 EMILIA BARCIA BONIFATTI</t>
+          <t>SAN MARCOS DEL SUR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.27182</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.86934</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-12.27866</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.86653</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIN.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
